--- a/www/download/COUNTRY.CZE.zdW16.xlsx
+++ b/www/download/COUNTRY.CZE.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>República Tcheca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>38.4337479053607</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>38.0106733970899</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>32.5804002827979</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>28.1623503171081</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>25.6449710211827</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>23.9311739437378</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>22.5586977314974</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>20.2235511342379</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>16.949209997322</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>18.9405059766767</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>19.0539703710761</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>17.6613229390561</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>19.5577599324084</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>19.5630782112304</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.7195914096574</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.859</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.846</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.877</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.838</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.829</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.923</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.989</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5.093</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>5.204</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5.057</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>5.043</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>5.065</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5.081</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>5.109</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.155</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.141</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.123</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.035</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4.053</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4.234</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>4.445</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.336</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4.251</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.255</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>4.296</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4.326</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8809.001</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8373.354</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8393.93</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8259.118</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8336.588</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8524.689</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8567.291</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>8728.184</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>8932.223</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>8753.092</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>8772.629</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>8794.115</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8770.942</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8781.362</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8846.175</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7503.32</t>
+          <t>9652796690.96939</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7128.206</t>
+          <t>9344095361.26279</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7068.005</t>
+          <t>9378703468.51897</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6859.997</t>
+          <t>9469858518.36153</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>9752203742.25813</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>9944743968.47545</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>10287997707.4335</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>10632696364.7064</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>10693970545.7108</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>9523384543.3126</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>9905618070.66193</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7360.311</t>
+          <t>10674426476.8044</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7355.239</t>
+          <t>10067004079.3767</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>7406.026</t>
+          <t>10320064940.8962</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7472.025</t>
+          <t>10366442861.7273</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1387753272.10883</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1387578585.03964</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1463068371.48028</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1574790867.97548</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1642334310.58446</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1746688626.03942</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1729821382.65352</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1772707239.63658</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1816916400.9827</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1663134295.50787</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1618281909.2813</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1719084363.22872</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1638820746.13568</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1739958568.76811</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1695391277.0964</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3578255.30414946</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3130087.42363526</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2657464.87699399</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2166538.32814451</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1830985.82035721</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1650715.4253461</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1433314.83256357</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1204843.14590898</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>984933.494474741</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1118893.07277762</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1116226.03507181</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1036736.95649959</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1089266.00215848</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1125635.69881921</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1118199.24171718</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>47315.1564714315</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>44025.0245066054</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>44024.3367362038</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>46797.2062992582</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>52762.6107905344</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>58053.70868539</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>60943.9563313098</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>69279.5220933551</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>76452.5083773456</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>66822.8834372117</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>73826.9816342066</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>79894.9487866291</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>77655.5580700066</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>76735.1311485396</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>77449.4554180746</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>87563.7987000966</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>83522.2962190524</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>84448.2833355864</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>92832.4703115953</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>105353.460967137</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>116037.114751144</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>126850.082089094</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>147064.010431385</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>161321.4563975</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>131292.84663333</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>150877.84335388</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>173355.03177668</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>159699.835554396</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>162765.041921846</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>164067.273101219</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4.40681124721684</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4.13715480827803</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3.83094648054544</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3.35613206775773</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3.24372428626892</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3.13084959301565</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3.18937878365419</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.17177175940011</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3.18502854390404</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3.4535585731146</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3.54875751732848</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.28152984079044</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.48812905093102</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3.25643813188235</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3.40725695651619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>38.4337479053607</t>
+          <t>333.999189428738</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>38.0106733970899</t>
+          <t>335.054652477969</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.5804002827979</t>
+          <t>354.836358836123</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28.1623503171081</t>
+          <t>390.275972405801</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.6449710211827</t>
+          <t>405.221484354396</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23.9311739437378</t>
+          <t>417.836104900921</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22.5586977314974</t>
+          <t>408.54427085114</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20.2235511342379</t>
+          <t>409.416338626041</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.949209997322</t>
+          <t>408.756015420214</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>18.9405059766767</t>
+          <t>383.551798490794</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>19.0539703710761</t>
+          <t>380.642347735785</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>17.6613229390561</t>
+          <t>406.387551115967</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>19.5577599324084</t>
+          <t>385.120083221282</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>19.5630782112304</t>
+          <t>405.026774017171</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>20.7195914096574</t>
+          <t>391.89830958517</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-324545877.762763</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-130950771.458189</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>143666617.801806</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>358545339.140334</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>724914077.474544</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>889740922.902984</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1112526427.46801</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1307784585.85939</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1591606609.23884</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1410832598.35675</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1290793656.99959</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1639536740.00908</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1364809315.22719</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1609336364.02639</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1720443697.36207</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-318477586.045402</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-110357854.161724</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>259380688.287645</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>490951916.849792</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>957566778.786478</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>1235508263.74987</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1508911444.61526</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1633954934.0666</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1937842002.09924</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1799915004.97394</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1835572837.69256</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>2209121925.67743</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1921052306.60866</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>2152174987.56413</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2342784049.23452</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>-6068291.71736092</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>-20592917.2964657</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>-115714070.48584</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-132406577.709457</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-232652701.311934</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>-345767340.846882</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>-396385017.147249</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>-326170348.207203</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>-346235392.8604</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>-389082406.617198</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>-544779180.692964</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-569585185.668356</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>-556242991.381469</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>-542838623.53774</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>-622340351.87245</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>1805.87057396461</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1721.22761901312</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>1714.19545888893</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1700.09367867224</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1719.64825447269</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>1726.01810387722</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1711.54670048723</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>1707.99151931711</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>1710.65559202608</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>1708.1704004022</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>1731.44974067671</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>1739.96042702876</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>1728.46863360241</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1723.97140535998</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1727.19655116618</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1812.7792221406</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1727.747286332</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1721.20687725753</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1707.10302086102</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1726.39115919445</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1731.72065296164</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>1717.24298377912</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1713.70693147464</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1716.38517688671</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1712.88683158427</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1734.66045203289</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1743.66704134355</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1731.78949914998</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>1728.25393606308</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1731.41060943835</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>27786.2361251875</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>31021.5317050104</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>35058.959764142</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>44496.0486928703</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>63982.5127098577</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>77662.1699874495</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>94127.9835373625</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>119228.197209327</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>142918.837729027</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>115774.295481564</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>130707.892213482</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>155485.526404928</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>149238.453814207</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>152000.140868781</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>161569.691185924</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2320818483.24051</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2301317640.40051</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2233634684.60315</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2353501883.07139</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2915756281.02428</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3279981031.31895</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3477295221.16395</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3809000259.9683</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3857979527.64587</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3449976228.83717</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3795363429.88095</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4296479170.08118</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>4264489917.15674</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>4422570399.12969</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>4621031343.99054</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>28441.8675523529</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31332.648044276</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>34811.5326908265</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>44290.3116809566</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>60588.9116208657</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>72524.3787024848</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>87618.5923075387</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>111072.194634525</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>131570.986932523</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>104880.229907377</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>120616.010625938</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>142574.543560858</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>134659.842748043</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>135260.279453731</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>142205.629391916</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8809.001</t>
+          <t>2085933409.02879</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8373.354</t>
+          <t>2214648329.67151</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8393.93</t>
+          <t>2341862684.55856</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8259.118</t>
+          <t>2684270716.2108</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8336.588</t>
+          <t>3223176527.95984</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8524.689</t>
+          <t>3596451475.8502</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8567.291</t>
+          <t>3930655692.54204</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8728.184</t>
+          <t>4408587411.73646</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8932.223</t>
+          <t>4589319178.13853</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8753.092</t>
+          <t>3933160504.17173</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>8772.629</t>
+          <t>4320107546.45775</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8794.115</t>
+          <t>5008222682.24267</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8770.942</t>
+          <t>4574689919.55081</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8781.362</t>
+          <t>4808879837.18025</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8846.175</t>
+          <t>4940309551.04066</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7503.32</t>
+          <t>-655.631427165439</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7128.206</t>
+          <t>-311.116339265583</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7068.005</t>
+          <t>247.427073315521</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6859.997</t>
+          <t>205.737011913687</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>3393.60108899201</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>5137.79128496477</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>6509.39122982384</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>8156.00257480217</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>11347.8507965036</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>10894.0655741869</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>10091.8815875436</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7360.311</t>
+          <t>12910.9828440699</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7355.239</t>
+          <t>14578.6110661639</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>7406.026</t>
+          <t>16739.8614150499</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7472.025</t>
+          <t>19364.0617940078</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11257.758</t>
+          <t>234885074.211726</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11015.456</t>
+          <t>86669310.7289942</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11229.144</t>
+          <t>-108227999.955405</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11340.269</t>
+          <t>-330768833.139412</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>11538.251</t>
+          <t>-307420246.935554</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11759.565</t>
+          <t>-316470444.531258</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12191.006</t>
+          <t>-453360471.378093</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>-599587151.768165</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>12903.225</t>
+          <t>-731339650.492659</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11690.224</t>
+          <t>-483184275.334565</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12088.646</t>
+          <t>-524744116.576803</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13152.564</t>
+          <t>-711743512.161496</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12328.74</t>
+          <t>-310200002.394069</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>12595.95</t>
+          <t>-386309438.050561</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>10366.443</t>
+          <t>-319278207.050124</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>29576.3765428</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>32703.182788</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>39038.0716308</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>46760.834418</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>57020.965194</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>64599.1293045</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>74386.8737448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>89679.0078044</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>110499.0144258</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>94431.8489803</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>94553.52165</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>105214.9381115</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>95392.2129348</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>95631.7804284</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>97338.1646445</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5215.895</t>
+          <t>0.0951142037597558</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4925.32</t>
+          <t>0.0981925032641166</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4889.279</t>
+          <t>0.0968497614088273</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4773.792</t>
+          <t>0.0966053011105065</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4884.052</t>
+          <t>0.0995561078051638</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4975.385</t>
+          <t>0.102199301153379</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4942.774</t>
+          <t>0.106308855235256</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5008.895</t>
+          <t>0.106850502677723</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5068.023</t>
+          <t>0.103973889497479</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4847.027</t>
+          <t>0.100963863599789</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4846.98</t>
+          <t>0.100325811315676</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4919.573</t>
+          <t>0.099610564912863</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>4895.176</t>
+          <t>0.0974925762420061</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>4865.366</t>
+          <t>0.0981091971275707</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4893.574</t>
+          <t>0.105020298950259</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>23812.2236284</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>26004.406438</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>32564.7625809</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>39719.6607316</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47276.559564</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>54288.8954405</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61795.8543792</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>74826.3245142</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>95393.7676302</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>82815.1582609</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>83397.42159</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>92051.0318287</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>85054.1169208</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>85596.2943009</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>82643.038955</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1639.897</t>
+          <t>27505.070351272</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1642.68</t>
+          <t>29963.52993018</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1757.676</t>
+          <t>37860.689840919</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1876.254</t>
+          <t>46713.171137596</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1927.784</t>
+          <t>55337.56730814</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2046.723</t>
+          <t>62839.47973198</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2030.977</t>
+          <t>71532.985157512</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2074.855</t>
+          <t>86554.098159179</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2154.922</t>
+          <t>109750.381303548</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2004.088</t>
+          <t>95479.045397567</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1948.724</t>
+          <t>97034.5751564</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2079.913</t>
+          <t>107288.836546311</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1976.967</t>
+          <t>98898.347084978</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2080.777</t>
+          <t>98911.850635509</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1695.391</t>
+          <t>95366.102107545</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>357.55</t>
+          <t>303872.26426</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>333.94</t>
+          <t>322838.6372376</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>302.12</t>
+          <t>385912.4163873</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>265.62</t>
+          <t>460142.0284204</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>261.53</t>
+          <t>530229.337704</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>252.53</t>
+          <t>591082.8709555</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>256.82</t>
+          <t>657880.4847976</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>256.43</t>
+          <t>797369.358772</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>252.86</t>
+          <t>1013990.6817318</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>269.59</t>
+          <t>912380.1138829</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>277.74</t>
+          <t>907078.0873175</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>253.88</t>
+          <t>990068.4144862</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>272.05</t>
+          <t>893574.9319144</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>255.93</t>
+          <t>896508.4538655</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>340.73</t>
+          <t>863711.6749155</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>35630.4488354732</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.751</t>
+          <t>36267.2359263789</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>37970.5887841003</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>39552.1848481384</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>41057.7278467106</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>42931.7337704416</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>45072.8131426085</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>46916.3911540872</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>48939.3927146812</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>46352.156442265</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>48106.001125696</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>49333.3486010795</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>49742.0418080212</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>49240.6877922559</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>48857.6886359964</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>31057.3463985819</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>31593.8844486885</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>32720.7967194919</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>33649.8204156789</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>34995.3616518899</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>36934.6242279016</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>38827.4030139661</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>40436.042503048</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>42535.5146769981</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>40162.3299418973</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>41345.2261776</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>42396.8466159451</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>42790.1570758402</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>42592.3055565262</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>42231.3842543353</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>28902.568459764</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>31700.333940736</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>37375.525451814</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>44452.159209152</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>52787.56910592</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>60408.256335385</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>69938.521220448</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>85199.316804602</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>105428.555093856</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>92117.421369233</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>91003.3450368</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>98621.274069353</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>87116.92217761</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>87955.724626824</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>90707.258306455</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7503320000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7128206000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7068005000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6859997000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6969614000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7215308000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7246877000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7395330000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7603847000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7406866000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>7361172000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7360311000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>7355239000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7406026000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7472025000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8809001224.2778</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8373354448.47941</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8393930062.8032</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8259118054.19751</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8336587532.54569</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8524689306.71469</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8567290901.21437</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8728183595.10938</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>8932222935.18434</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8753091513.55203</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8772628917.64785</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8794114976.33455</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8770942322.6599</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8781361944.37269</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8846175028.06073</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5215895068.51339</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4925319895.33369</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4889278779.13523</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4773792200.30514</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4884051512.68133</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4975384561.5243</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4942773963.50499</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5008894566.04545</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5068023132.13998</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4847027325.43213</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4846979961.55058</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4919573132.37706</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4895176110.62757</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4865366219.61712</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4893574075.36141</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4859390</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4846400</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4876770</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4838090</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4828910</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4922670</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4988980</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5093160</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5204090</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5110140</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5057260</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5043460</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>5064670</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>5081060</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>5109230</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4154960</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4141350</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4123220</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4035070</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4052930</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4180320</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4234110</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4329840</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4444990</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4336140</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>4251450</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4230160</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>4255350</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4295910</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>4326100</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8809001224.2778</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8373354448.47941</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8393930062.8032</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8259118054.19751</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8336587532.54569</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8524689306.71469</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8567290901.21437</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8728183595.10938</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8932222935.18434</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>8753091513.55203</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>8772628917.64785</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8794114976.33455</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8770942322.6599</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8781361944.37269</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8846175028.06073</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7503320000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7128206000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7068005000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6859997000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6969614000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7215308000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7246877000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7395330000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7603847000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7406866000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7361172000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7360311000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7355239000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>7406026000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7472025000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>137783.3099452</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>151346.0164176</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>182446.193061</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>227352.7929276</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>274328.951052</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>312337.707192</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>370516.8223576</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>456066.7381697</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>566629.3002162</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>467214.9208103</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>485891.697095</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>548193.7583843</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>491599.3975398</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>492524.4328098</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>492771.782905</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>56407.6395916</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>61663.864134</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>75236.2149858</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>91165.331412</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>108125.136804</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>123247.7356495</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>141471.5085944</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>171753.4164472</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>215178.9375774</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>187596.4667668</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>188037.9222925</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>205910.1128805</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>186015.2702852</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>186867.5757735</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>186073.360414</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>410947.437317005</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>416255.360298232</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>412712.874200826</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>413769.953693106</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>416129.737277957</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>419298.68164638</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>425236.226235358</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>445722.636057738</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>456707.275649841</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>450228.100568903</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>449694.3426532</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>449640.768363888</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>446694.290502901</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>449457.951528099</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>454006.786561931</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
